--- a/data/trans_dic/P14B23-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P14B23-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,25</t>
+          <t>3,29; 6,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,81</t>
+          <t>2,36; 4,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,93; 10,62</t>
+          <t>5,97; 10,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,13; 16,17</t>
+          <t>12,24; 16,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,95; 15,33</t>
+          <t>10,97; 15,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,57; 15,36</t>
+          <t>11,61; 15,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,78; 11,34</t>
+          <t>8,86; 11,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 10,48</t>
+          <t>7,61; 10,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,77; 12,73</t>
+          <t>9,73; 12,53</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,72</t>
+          <t>1,36; 2,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,53</t>
+          <t>1,26; 2,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,76</t>
+          <t>1,91; 3,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,16</t>
+          <t>4,06; 6,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,05</t>
+          <t>4,06; 6,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,59</t>
+          <t>4,59; 7,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,06</t>
+          <t>2,84; 4,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,01</t>
+          <t>2,81; 3,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 5,29</t>
+          <t>3,67; 5,33</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,44</t>
+          <t>0,16; 1,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,04</t>
+          <t>1,79; 4,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,96</t>
+          <t>0,81; 3,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,07</t>
+          <t>0,73; 3,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,64</t>
+          <t>2,87; 5,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,38</t>
+          <t>0,61; 2,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,82</t>
+          <t>0,54; 1,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,76</t>
+          <t>2,67; 4,62</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,15</t>
+          <t>1,96; 3,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,51</t>
+          <t>1,52; 2,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,49</t>
+          <t>2,73; 4,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,12</t>
+          <t>7,08; 8,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 7,6</t>
+          <t>5,88; 7,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 8,2</t>
+          <t>6,02; 8,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 5,85</t>
+          <t>4,73; 5,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 4,93</t>
+          <t>3,95; 5,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,15</t>
+          <t>4,75; 6,18</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33053; 60867</t>
+          <t>32073; 60343</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17189; 36260</t>
+          <t>17797; 37364</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30526; 54684</t>
+          <t>30742; 52651</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>161312; 215002</t>
+          <t>162746; 213258</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>108910; 152468</t>
+          <t>109115; 153815</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87431; 116050</t>
+          <t>87733; 114850</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>202262; 261171</t>
+          <t>204140; 264205</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>133056; 183214</t>
+          <t>133136; 181930</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>124078; 161709</t>
+          <t>123622; 159145</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26830; 53452</t>
+          <t>26782; 53464</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26620; 52545</t>
+          <t>26209; 52197</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43582; 86035</t>
+          <t>43707; 86655</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70671; 108166</t>
+          <t>71253; 109710</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79121; 120282</t>
+          <t>80699; 121135</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>99950; 169830</t>
+          <t>102799; 166590</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>104191; 150953</t>
+          <t>105403; 150257</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>112122; 162839</t>
+          <t>114341; 161833</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>161817; 239666</t>
+          <t>166244; 241373</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 9742</t>
+          <t>0; 11520</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>883; 7874</t>
+          <t>879; 8329</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11805; 32599</t>
+          <t>11556; 32090</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3660; 18149</t>
+          <t>3736; 17451</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3963; 16854</t>
+          <t>4035; 16608</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19210; 37217</t>
+          <t>18951; 36706</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5581; 22379</t>
+          <t>5732; 22459</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5889; 19968</t>
+          <t>5942; 20210</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35099; 62179</t>
+          <t>34962; 60410</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>66926; 107593</t>
+          <t>67120; 106523</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51867; 84710</t>
+          <t>51280; 83160</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96838; 154912</t>
+          <t>94093; 150077</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>253981; 323136</t>
+          <t>250917; 316222</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>206528; 268610</t>
+          <t>207700; 268764</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>215124; 299743</t>
+          <t>219864; 300898</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>327757; 407477</t>
+          <t>329341; 408061</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>267417; 340988</t>
+          <t>273168; 346345</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>337457; 436691</t>
+          <t>337446; 439091</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P14B23-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P14B23-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,2</t>
+          <t>3,32; 6,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,95</t>
+          <t>2,34; 4,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,97; 10,22</t>
+          <t>5,48; 9,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,24; 16,04</t>
+          <t>12,2; 16,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,97; 15,46</t>
+          <t>11,0; 15,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,61; 15,2</t>
+          <t>11,79; 15,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 11,47</t>
+          <t>8,86; 11,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 10,4</t>
+          <t>7,57; 10,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,73; 12,53</t>
+          <t>9,61; 12,42</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,72</t>
+          <t>1,34; 2,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,51</t>
+          <t>1,32; 2,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,78</t>
+          <t>2,48; 4,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,25</t>
+          <t>4,02; 6,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,09</t>
+          <t>4,04; 6,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,44</t>
+          <t>6,25; 8,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,04</t>
+          <t>2,86; 4,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 3,98</t>
+          <t>2,86; 4,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 5,33</t>
+          <t>4,6; 5,86</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,52</t>
+          <t>0,16; 1,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,96</t>
+          <t>1,86; 5,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,8</t>
+          <t>0,78; 3,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,02</t>
+          <t>0,71; 2,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,56</t>
+          <t>3,08; 5,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,39</t>
+          <t>0,59; 2,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,84</t>
+          <t>0,56; 1,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,62</t>
+          <t>2,79; 4,78</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,12</t>
+          <t>1,99; 3,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,46</t>
+          <t>1,54; 2,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,35</t>
+          <t>3,22; 4,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 8,93</t>
+          <t>7,16; 9,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,61</t>
+          <t>5,88; 7,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,24</t>
+          <t>7,28; 8,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 5,86</t>
+          <t>4,79; 5,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,01</t>
+          <t>3,97; 4,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,18</t>
+          <t>5,48; 6,52</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40776</t>
+          <t>42407</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>100390</t>
+          <t>110466</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>141167</t>
+          <t>152873</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32073; 60343</t>
+          <t>32286; 60127</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17797; 37364</t>
+          <t>17651; 36535</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30742; 52651</t>
+          <t>31697; 54957</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>162746; 213258</t>
+          <t>162159; 213931</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>109115; 153815</t>
+          <t>109427; 152322</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87733; 114850</t>
+          <t>96893; 125268</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>204140; 264205</t>
+          <t>204019; 261373</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>133136; 181930</t>
+          <t>132446; 180695</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>123622; 159145</t>
+          <t>134571; 173924</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65215</t>
+          <t>70354</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>141036</t>
+          <t>157492</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>206251</t>
+          <t>227846</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26782; 53464</t>
+          <t>26278; 52479</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26209; 52197</t>
+          <t>27374; 51078</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43707; 86655</t>
+          <t>55209; 92563</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71253; 109710</t>
+          <t>70588; 109797</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80699; 121135</t>
+          <t>80235; 121096</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>102799; 166590</t>
+          <t>135786; 180078</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>105403; 150257</t>
+          <t>106288; 153302</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>114341; 161833</t>
+          <t>116200; 165291</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>166244; 241373</t>
+          <t>202567; 258013</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19811</t>
+          <t>22457</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26414</t>
+          <t>30704</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46226</t>
+          <t>53161</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 11520</t>
+          <t>0; 12942</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>879; 8329</t>
+          <t>888; 7964</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11556; 32090</t>
+          <t>13225; 36065</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3736; 17451</t>
+          <t>3595; 17085</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4035; 16608</t>
+          <t>3911; 16106</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18951; 36706</t>
+          <t>22638; 41330</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5732; 22459</t>
+          <t>5502; 22383</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5942; 20210</t>
+          <t>6111; 20660</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34962; 60410</t>
+          <t>40351; 69142</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125802</t>
+          <t>135218</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>267841</t>
+          <t>298662</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>393643</t>
+          <t>433879</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67120; 106523</t>
+          <t>67892; 105304</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51280; 83160</t>
+          <t>52082; 84015</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94093; 150077</t>
+          <t>113334; 163434</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>250917; 316222</t>
+          <t>253762; 321395</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>207700; 268764</t>
+          <t>207567; 270538</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>219864; 300898</t>
+          <t>271606; 328891</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>329341; 408061</t>
+          <t>333062; 405892</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>273168; 346345</t>
+          <t>274125; 343741</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>337446; 439091</t>
+          <t>397064; 472760</t>
         </is>
       </c>
     </row>
